--- a/assigned_sus-preferences.xlsx
+++ b/assigned_sus-preferences.xlsx
@@ -732,7 +732,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -786,7 +786,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -840,7 +840,7 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/assigned_sus-preferences.xlsx
+++ b/assigned_sus-preferences.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
           <t>ASSIGNED BUCKET</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ASSIGNED BUCKET (iteration 1)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ASSIGNED BUCKET (iteration 2)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -489,7 +499,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -518,6 +534,12 @@
       <c r="G3" t="n">
         <v>2</v>
       </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -543,6 +565,12 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -570,7 +598,13 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +631,13 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -626,6 +666,12 @@
       <c r="G7" t="n">
         <v>2</v>
       </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -651,7 +697,13 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -678,7 +730,13 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +763,13 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +796,13 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -759,7 +829,13 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -786,7 +862,13 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +895,13 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -840,7 +928,13 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -867,7 +961,13 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -894,7 +994,13 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +1027,13 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -948,7 +1060,13 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -975,7 +1093,13 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1002,7 +1126,13 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/assigned_sus-preferences.xlsx
+++ b/assigned_sus-preferences.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ASSIGNED BUCKET</t>
+          <t>priority 4</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ASSIGNED BUCKET (iteration 1)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ASSIGNED BUCKET (iteration 2)</t>
         </is>
       </c>
     </row>
@@ -490,22 +485,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -532,12 +524,9 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -565,13 +554,10 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -598,13 +584,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -631,13 +614,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -664,13 +644,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -697,13 +674,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -730,13 +704,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -763,13 +734,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -796,13 +764,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -829,13 +794,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -862,13 +824,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -895,13 +854,10 @@
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -928,13 +884,10 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -961,13 +914,10 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -994,13 +944,10 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1027,13 +974,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1060,13 +1004,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1093,13 +1034,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1126,13 +1064,10 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
